--- a/行動予定表_1026.xlsx
+++ b/行動予定表_1026.xlsx
@@ -1144,7 +1144,7 @@
     <row r="18" ht="30" customHeight="1" s="29">
       <c r="A18" s="53" t="inlineStr">
         <is>
-          <t>13:30　坂根様邸（習志野市藤崎7-7-5）請求書持参　竣工金1,250,000円（175万円－手付金50万円）　※時間は坂根様に確認</t>
+          <t xml:space="preserve">　坂根様邸：請求書は渡し済み。ガラスの部分が当初の予定と相違があり、アベルコに確認中（回答待ち）</t>
         </is>
       </c>
       <c r="B18" s="11" t="n"/>
@@ -1489,7 +1489,7 @@
       <c r="K35" s="58" t="inlineStr">
         <is>
           <t>手付金500,000円済
-請求書10/26持参
+請求書渡し済
 10/30(金)まで入金予定</t>
         </is>
       </c>
@@ -1640,7 +1640,8 @@
         <is>
           <t>秋元さんと連絡が付きました。山川様邸、吉田様邸の見積り依頼は明日メールアドレスをもらったら連絡します。概要は共有済みです。現調日が確定しましたら共有させていただきます。
 ・夏目様(アベルコ)へのメールは、今後は署名を3行(会社名／氏名／携帯・TEL)にし、香澄のフェンス材料の回答(10/28まで)の一文を添えます。
-・青木様の利益は手付金を引いた数字だったため「原価確認中」にしました。坂根様は解体費121,000円を引いた629,000円です(産廃費の含有は確認中)。</t>
+・青木様の利益は手付金を引いた数字だったため「原価確認中」にしました。坂根様は解体費121,000円を引いた629,000円です(産廃費の含有は確認中)。
+・坂根様邸のガラスの部分が当初の予定と少し相違があるため、アベルコに確認中です。回答が来たら報告します。</t>
         </is>
       </c>
       <c r="B44" s="63" t="n"/>
